--- a/ficha/planilha-controle-financeiro.xlsx
+++ b/ficha/planilha-controle-financeiro.xlsx
@@ -13,7 +13,7 @@
     <sheet name="Configuração" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Lançamentos'!$A$1:$S$300</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Lançamentos'!$A$1:$AA$300</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -552,7 +552,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:J42"/>
+  <dimension ref="B2:J60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="2" max="2"/>
@@ -644,13 +644,13 @@
     </row>
     <row r="10">
       <c r="B10" s="8">
-        <f>IFERROR(QUERY(Dados!A2:AG,"select AF, count(A), sum(I) where A is not null and J = 'BRL' group by AF order by sum(I) desc label AF 'Categoria', count(A) 'Qtd', sum(I) 'Valor (R$)'",0),"Sem lançamentos ainda")</f>
+        <f>IFERROR(QUERY(Dados!A2:AO,"select AF, count(A), sum(I) where A is not null and J = 'BRL' group by AF order by sum(I) desc label AF 'Categoria', count(A) 'Qtd', sum(I) 'Valor (R$)'",0),"Sem lançamentos ainda")</f>
         <v/>
       </c>
       <c r="C10" s="8" t="n"/>
       <c r="D10" s="8" t="n"/>
       <c r="F10" s="8">
-        <f>IFERROR(QUERY(Dados!A2:AG,"select K, count(A), sum(I) where A is not null and J = 'BRL' group by K order by sum(I) desc label K 'Forma', count(A) 'Qtd', sum(I) 'Valor (R$)'",0),"Sem lançamentos ainda")</f>
+        <f>IFERROR(QUERY(Dados!A2:AO,"select K, count(A), sum(I) where A is not null and J = 'BRL' group by K order by sum(I) desc label K 'Forma', count(A) 'Qtd', sum(I) 'Valor (R$)'",0),"Sem lançamentos ainda")</f>
         <v/>
       </c>
       <c r="G10" s="8" t="n"/>
@@ -726,13 +726,13 @@
     </row>
     <row r="28">
       <c r="B28" s="8">
-        <f>IFERROR(QUERY(Dados!A2:AG,"select U, count(A), sum(I) where A is not null and J = 'BRL' group by U order by sum(I) desc label U 'Responsável', count(A) 'Qtd', sum(I) 'Valor (R$)'",0),"Sem lançamentos ainda")</f>
+        <f>IFERROR(QUERY(Dados!A2:AO,"select U, count(A), sum(I) where A is not null and J = 'BRL' group by U order by sum(I) desc label U 'Responsável', count(A) 'Qtd', sum(I) 'Valor (R$)'",0),"Sem lançamentos ainda")</f>
         <v/>
       </c>
       <c r="C28" s="8" t="n"/>
       <c r="D28" s="8" t="n"/>
       <c r="F28" s="8">
-        <f>IFERROR(QUERY(Dados!A2:AG,"select year(B), month(B)+1, sum(I) where A is not null and J = 'BRL' group by year(B), month(B)+1 order by year(B) desc, month(B)+1 desc label year(B) 'Ano', month(B)+1 'Mês', sum(I) 'Valor (R$)'",0),"Sem lançamentos ainda")</f>
+        <f>IFERROR(QUERY(Dados!A2:AO,"select year(B), month(B)+1, sum(I) where A is not null and J = 'BRL' group by year(B), month(B)+1 order by year(B) desc, month(B)+1 desc label year(B) 'Ano', month(B)+1 'Mês', sum(I) 'Valor (R$)'",0),"Sem lançamentos ainda")</f>
         <v/>
       </c>
       <c r="G28" s="8" t="n"/>
@@ -793,6 +793,63 @@
     <row r="42">
       <c r="D42" s="9" t="n"/>
       <c r="H42" s="9" t="n"/>
+    </row>
+    <row r="45">
+      <c r="B45" s="7" t="inlineStr">
+        <is>
+          <t>Cartão por bandeira</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="B46" s="8">
+        <f>IFERROR(QUERY(Dados!A2:AO,"select AI, count(A), sum(I) where A is not null and J = 'BRL' and AI is not null group by AI order by sum(I) desc label AI 'Bandeira', count(A) 'Qtd', sum(I) 'Valor (R$)'",0),"Sem cartão ainda")</f>
+        <v/>
+      </c>
+      <c r="C46" s="8" t="n"/>
+      <c r="D46" s="8" t="n"/>
+    </row>
+    <row r="47">
+      <c r="D47" s="9" t="n"/>
+    </row>
+    <row r="48">
+      <c r="D48" s="9" t="n"/>
+    </row>
+    <row r="49">
+      <c r="D49" s="9" t="n"/>
+    </row>
+    <row r="50">
+      <c r="D50" s="9" t="n"/>
+    </row>
+    <row r="51">
+      <c r="D51" s="9" t="n"/>
+    </row>
+    <row r="52">
+      <c r="D52" s="9" t="n"/>
+    </row>
+    <row r="53">
+      <c r="D53" s="9" t="n"/>
+    </row>
+    <row r="54">
+      <c r="D54" s="9" t="n"/>
+    </row>
+    <row r="55">
+      <c r="D55" s="9" t="n"/>
+    </row>
+    <row r="56">
+      <c r="D56" s="9" t="n"/>
+    </row>
+    <row r="57">
+      <c r="D57" s="9" t="n"/>
+    </row>
+    <row r="58">
+      <c r="D58" s="9" t="n"/>
+    </row>
+    <row r="59">
+      <c r="D59" s="9" t="n"/>
+    </row>
+    <row r="60">
+      <c r="D60" s="9" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -805,7 +862,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S301"/>
+  <dimension ref="A1:AA301"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -827,6 +884,14 @@
     <col width="16" customWidth="1" min="17" max="17"/>
     <col width="18" customWidth="1" min="18" max="18"/>
     <col width="40" customWidth="1" min="19" max="19"/>
+    <col width="16" customWidth="1" min="20" max="20"/>
+    <col width="12" customWidth="1" min="21" max="21"/>
+    <col width="8" customWidth="1" min="22" max="22"/>
+    <col width="9" customWidth="1" min="23" max="23"/>
+    <col width="12" customWidth="1" min="24" max="24"/>
+    <col width="12" customWidth="1" min="25" max="25"/>
+    <col width="10" customWidth="1" min="26" max="26"/>
+    <col width="30" customWidth="1" min="27" max="27"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
@@ -925,10 +990,50 @@
           <t>Observações</t>
         </is>
       </c>
+      <c r="T1" s="10" t="inlineStr">
+        <is>
+          <t>Documento</t>
+        </is>
+      </c>
+      <c r="U1" s="10" t="inlineStr">
+        <is>
+          <t>Bandeira</t>
+        </is>
+      </c>
+      <c r="V1" s="10" t="inlineStr">
+        <is>
+          <t>Final</t>
+        </is>
+      </c>
+      <c r="W1" s="10" t="inlineStr">
+        <is>
+          <t>Parcelas</t>
+        </is>
+      </c>
+      <c r="X1" s="10" t="inlineStr">
+        <is>
+          <t>NSU</t>
+        </is>
+      </c>
+      <c r="Y1" s="10" t="inlineStr">
+        <is>
+          <t>Autorização</t>
+        </is>
+      </c>
+      <c r="Z1" s="10" t="inlineStr">
+        <is>
+          <t>Nº NF</t>
+        </is>
+      </c>
+      <c r="AA1" s="10" t="inlineStr">
+        <is>
+          <t>Paciente no Amigo</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2">
-        <f>IFERROR(QUERY(Dados!A2:AG,"select A, B, E, F, G, I, J, K, L, AF, AG, AB, AE, R, S, O, U, T, V where A is not null order by A desc",0),"")</f>
+        <f>IFERROR(QUERY(Dados!A2:AO,"select A, B, E, F, G, I, J, K, L, AF, AG, AB, AE, R, S, O, U, T, V, AH, AI, AJ, AM, AK, AL, AN, AO where A is not null order by A desc",0),"")</f>
         <v/>
       </c>
       <c r="B2" s="11" t="n"/>
@@ -2131,8 +2236,8 @@
       <c r="F301" s="12" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:S300"/>
-  <conditionalFormatting sqref="A2:S300">
+  <autoFilter ref="A1:AA300"/>
+  <conditionalFormatting sqref="A2:AA300">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>ISNUMBER(SEARCH("diverg",$N2))</formula>
     </cfRule>
